--- a/artfynd/A 43939-2020 artfynd.xlsx
+++ b/artfynd/A 43939-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43939-2020 artfynd.xlsx
+++ b/artfynd/A 43939-2020 artfynd.xlsx
@@ -3174,10 +3174,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118691564</v>
+        <v>118691578</v>
       </c>
       <c r="B22" t="n">
-        <v>97750</v>
+        <v>96807</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3190,38 +3190,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220093</v>
+        <v>221941</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Yttervik,  NO om, vid Ryfjällsstigen, Ly lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524944</v>
+        <v>524815</v>
       </c>
       <c r="R22" t="n">
-        <v>7279425</v>
+        <v>7279331</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3267,7 +3263,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>fuktig barrskog av högörttyp</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3285,10 +3281,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118691578</v>
+        <v>118691564</v>
       </c>
       <c r="B23" t="n">
-        <v>96807</v>
+        <v>97750</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3301,34 +3297,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>220093</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Yttervik,  NO om, vid Ryfjällsstigen, Ly lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524815</v>
+        <v>524944</v>
       </c>
       <c r="R23" t="n">
-        <v>7279331</v>
+        <v>7279425</v>
       </c>
       <c r="S23" t="n">
         <v>50</v>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>fuktig barrskog av högörttyp</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>

--- a/artfynd/A 43939-2020 artfynd.xlsx
+++ b/artfynd/A 43939-2020 artfynd.xlsx
@@ -3174,10 +3174,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118691578</v>
+        <v>118691562</v>
       </c>
       <c r="B22" t="n">
-        <v>96807</v>
+        <v>98180</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3190,21 +3190,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221941</v>
+        <v>219880</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3214,10 +3214,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524815</v>
+        <v>524944</v>
       </c>
       <c r="R22" t="n">
-        <v>7279331</v>
+        <v>7279425</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>fuktig barrskog av högörttyp</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118691564</v>
+        <v>118691563</v>
       </c>
       <c r="B23" t="n">
-        <v>97750</v>
+        <v>104925</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3297,28 +3297,24 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220093</v>
+        <v>221725</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Yttervik,  NO om, vid Ryfjällsstigen, Ly lm</t>
@@ -3392,10 +3388,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118691562</v>
+        <v>118691564</v>
       </c>
       <c r="B24" t="n">
-        <v>98180</v>
+        <v>97750</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3408,24 +3404,28 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219880</v>
+        <v>220093</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Yttervik,  NO om, vid Ryfjällsstigen, Ly lm</t>
@@ -3499,10 +3499,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118691563</v>
+        <v>118691578</v>
       </c>
       <c r="B25" t="n">
-        <v>104925</v>
+        <v>96807</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3515,21 +3515,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221725</v>
+        <v>221941</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524944</v>
+        <v>524815</v>
       </c>
       <c r="R25" t="n">
-        <v>7279425</v>
+        <v>7279331</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>fuktig barrskog av högörttyp</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>

--- a/artfynd/A 43939-2020 artfynd.xlsx
+++ b/artfynd/A 43939-2020 artfynd.xlsx
@@ -3388,10 +3388,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118691564</v>
+        <v>118691578</v>
       </c>
       <c r="B24" t="n">
-        <v>97750</v>
+        <v>96807</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3404,38 +3404,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220093</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Yttervik,  NO om, vid Ryfjällsstigen, Ly lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524944</v>
+        <v>524815</v>
       </c>
       <c r="R24" t="n">
-        <v>7279425</v>
+        <v>7279331</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3481,7 +3477,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>fuktig barrskog av högörttyp</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3499,10 +3495,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118691578</v>
+        <v>118691564</v>
       </c>
       <c r="B25" t="n">
-        <v>96807</v>
+        <v>97750</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3515,34 +3511,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>220093</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Yttervik,  NO om, vid Ryfjällsstigen, Ly lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524815</v>
+        <v>524944</v>
       </c>
       <c r="R25" t="n">
-        <v>7279331</v>
+        <v>7279425</v>
       </c>
       <c r="S25" t="n">
         <v>50</v>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>fuktig barrskog av högörttyp</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>

--- a/artfynd/A 43939-2020 artfynd.xlsx
+++ b/artfynd/A 43939-2020 artfynd.xlsx
@@ -3174,10 +3174,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118691562</v>
+        <v>118691578</v>
       </c>
       <c r="B22" t="n">
-        <v>98180</v>
+        <v>96814</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3190,21 +3190,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219880</v>
+        <v>221941</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3214,10 +3214,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524944</v>
+        <v>524815</v>
       </c>
       <c r="R22" t="n">
-        <v>7279425</v>
+        <v>7279331</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>fuktig barrskog av högörttyp</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3284,7 +3284,7 @@
         <v>118691563</v>
       </c>
       <c r="B23" t="n">
-        <v>104925</v>
+        <v>104932</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3388,10 +3388,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118691578</v>
+        <v>118691562</v>
       </c>
       <c r="B24" t="n">
-        <v>96807</v>
+        <v>98187</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3404,21 +3404,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>219880</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524815</v>
+        <v>524944</v>
       </c>
       <c r="R24" t="n">
-        <v>7279331</v>
+        <v>7279425</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>fuktig barrskog av högörttyp</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3498,7 +3498,7 @@
         <v>118691564</v>
       </c>
       <c r="B25" t="n">
-        <v>97750</v>
+        <v>97757</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 43939-2020 artfynd.xlsx
+++ b/artfynd/A 43939-2020 artfynd.xlsx
@@ -3174,10 +3174,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118691578</v>
+        <v>118691562</v>
       </c>
       <c r="B22" t="n">
-        <v>96814</v>
+        <v>98187</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3190,21 +3190,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221941</v>
+        <v>219880</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3214,10 +3214,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524815</v>
+        <v>524944</v>
       </c>
       <c r="R22" t="n">
-        <v>7279331</v>
+        <v>7279425</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>fuktig barrskog av högörttyp</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3281,10 +3281,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118691563</v>
+        <v>118691564</v>
       </c>
       <c r="B23" t="n">
-        <v>104932</v>
+        <v>97757</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3297,24 +3297,28 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221725</v>
+        <v>220093</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Yttervik,  NO om, vid Ryfjällsstigen, Ly lm</t>
@@ -3388,10 +3392,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118691562</v>
+        <v>118691578</v>
       </c>
       <c r="B24" t="n">
-        <v>98187</v>
+        <v>96814</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3404,21 +3408,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219880</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3428,10 +3432,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524944</v>
+        <v>524815</v>
       </c>
       <c r="R24" t="n">
-        <v>7279425</v>
+        <v>7279331</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3477,7 +3481,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>fuktig barrskog av högörttyp</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3495,10 +3499,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118691564</v>
+        <v>118691563</v>
       </c>
       <c r="B25" t="n">
-        <v>97757</v>
+        <v>104932</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3511,28 +3515,24 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220093</v>
+        <v>221725</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Yttervik,  NO om, vid Ryfjällsstigen, Ly lm</t>
